--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_06-10-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_06-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AABF013-B9C3-4150-B5F0-73FD45988449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7E6AA0-FB6C-4437-B133-A18930A6FA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31395" yWindow="1440" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29895" yWindow="3000" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="271">
   <si>
     <t>SKU</t>
   </si>
@@ -788,6 +788,51 @@
   </si>
   <si>
     <t>£596.8</t>
+  </si>
+  <si>
+    <t>£14.11</t>
+  </si>
+  <si>
+    <t>£17.03</t>
+  </si>
+  <si>
+    <t>£19.93</t>
+  </si>
+  <si>
+    <t>£21.82</t>
+  </si>
+  <si>
+    <t>£26.80</t>
+  </si>
+  <si>
+    <t>£30.17</t>
+  </si>
+  <si>
+    <t>£30.73</t>
+  </si>
+  <si>
+    <t>£34.68</t>
+  </si>
+  <si>
+    <t>£36.08</t>
+  </si>
+  <si>
+    <t>£37.18</t>
+  </si>
+  <si>
+    <t>£45.43</t>
+  </si>
+  <si>
+    <t>£45.86</t>
+  </si>
+  <si>
+    <t>£53.70</t>
+  </si>
+  <si>
+    <t>£53.14</t>
+  </si>
+  <si>
+    <t>£53.56</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1309,7 @@
         <v>179</v>
       </c>
       <c r="Q2" t="s">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="R2" t="s">
         <v>197</v>
@@ -1320,7 +1365,7 @@
         <v>179</v>
       </c>
       <c r="Q3" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="R3" t="s">
         <v>198</v>
@@ -1376,7 +1421,7 @@
         <v>179</v>
       </c>
       <c r="Q4" t="s">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="R4" t="s">
         <v>199</v>
@@ -1432,7 +1477,7 @@
         <v>179</v>
       </c>
       <c r="Q5" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="R5" t="s">
         <v>200</v>
@@ -1488,7 +1533,7 @@
         <v>179</v>
       </c>
       <c r="Q6" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="R6" t="s">
         <v>201</v>
@@ -1544,7 +1589,7 @@
         <v>179</v>
       </c>
       <c r="Q7" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="R7" t="s">
         <v>202</v>
@@ -1600,7 +1645,7 @@
         <v>179</v>
       </c>
       <c r="Q8" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="R8" t="s">
         <v>203</v>
@@ -1656,7 +1701,7 @@
         <v>179</v>
       </c>
       <c r="Q9" t="s">
-        <v>179</v>
+        <v>263</v>
       </c>
       <c r="R9" t="s">
         <v>204</v>
@@ -1712,7 +1757,7 @@
         <v>179</v>
       </c>
       <c r="Q10" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="R10" t="s">
         <v>205</v>
@@ -1768,7 +1813,7 @@
         <v>179</v>
       </c>
       <c r="Q11" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="R11" t="s">
         <v>206</v>
@@ -1824,7 +1869,7 @@
         <v>179</v>
       </c>
       <c r="Q12" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="R12" t="s">
         <v>88</v>
@@ -1880,7 +1925,7 @@
         <v>179</v>
       </c>
       <c r="Q13" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="R13" t="s">
         <v>207</v>
@@ -1936,7 +1981,7 @@
         <v>179</v>
       </c>
       <c r="Q14" t="s">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="R14" t="s">
         <v>88</v>
@@ -1992,7 +2037,7 @@
         <v>179</v>
       </c>
       <c r="Q15" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="R15" t="s">
         <v>88</v>
@@ -2048,7 +2093,7 @@
         <v>179</v>
       </c>
       <c r="Q16" t="s">
-        <v>179</v>
+        <v>270</v>
       </c>
       <c r="R16" t="s">
         <v>208</v>
